--- a/templates/INFRA ADV II SB - template.xlsx
+++ b/templates/INFRA ADV II SB - template.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="20370" yWindow="-60" windowWidth="20730" windowHeight="11040" tabRatio="711" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Email" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Email" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="DataAnálise">Email!$A$7</definedName>
@@ -1405,96 +1405,96 @@
     <row r="17" ht="15.95" customFormat="1" customHeight="1" s="34">
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C17" s="36" t="n">
-        <v>1.083365447777</v>
+        <v>1.052403895916</v>
       </c>
       <c r="D17" s="37" t="n">
-        <v>-0.002491418392641109</v>
+        <v>-0.000590912221664075</v>
       </c>
       <c r="E17" s="37" t="n">
         <v>0.0005426623598601132</v>
       </c>
       <c r="F17" s="38" t="n">
-        <v>-4.591102270817795</v>
+        <v>-1.088913227400551</v>
       </c>
     </row>
     <row r="18" ht="15.95" customFormat="1" customHeight="1" s="34">
       <c r="B18" s="39" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="C18" s="40" t="n">
-        <v>1.086071305804</v>
+        <v>1.053026141933</v>
       </c>
       <c r="D18" s="41" t="n">
-        <v>0.0004790693136560442</v>
+        <v>0.0007238679375654034</v>
       </c>
       <c r="E18" s="41" t="n">
         <v>0.0005426623598601132</v>
       </c>
       <c r="F18" s="42" t="n">
-        <v>0.8828128668801316</v>
+        <v>1.33391956234444</v>
       </c>
     </row>
     <row r="19" ht="15.95" customFormat="1" customHeight="1" s="34">
       <c r="B19" s="39" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="C19" s="40" t="n">
-        <v>1.085551251511</v>
+        <v>1.052264441442</v>
       </c>
       <c r="D19" s="41" t="n">
-        <v>-0.0001808729034996626</v>
+        <v>0.001637133011826775</v>
       </c>
       <c r="E19" s="41" t="n">
         <v>0.0005426623598601132</v>
       </c>
       <c r="F19" s="42" t="n">
-        <v>-0.3333065214736613</v>
+        <v>3.016853817259027</v>
       </c>
     </row>
     <row r="20" ht="15.95" customFormat="1" customHeight="1" s="34">
       <c r="B20" s="39" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="C20" s="40" t="n">
-        <v>1.085747633838</v>
+        <v>1.050544560262</v>
       </c>
       <c r="D20" s="41" t="n">
-        <v>0.001278877789573807</v>
+        <v>-0.01488804937845356</v>
       </c>
       <c r="E20" s="41" t="n">
         <v>0.0005426623598601132</v>
       </c>
       <c r="F20" s="42" t="n">
-        <v>2.356673106834744</v>
+        <v>-27.4351981631661</v>
       </c>
     </row>
     <row r="21" ht="15.95" customFormat="1" customHeight="1" s="34">
       <c r="B21" s="39" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="C21" s="40" t="n">
-        <v>1.084360868807</v>
+        <v>1.066421496155</v>
       </c>
       <c r="D21" s="41" t="n">
-        <v>0.0007176543869238383</v>
+        <v>-0.006344609905555298</v>
       </c>
       <c r="E21" s="41" t="n">
         <v>0.0005426623598601132</v>
       </c>
       <c r="F21" s="42" t="n">
-        <v>1.322469439577188</v>
+        <v>-11.69163438420679</v>
       </c>
     </row>
     <row r="22" ht="15.95" customHeight="1">
@@ -1534,18 +1534,18 @@
     <row r="24" ht="15.95" customFormat="1" customHeight="1" s="45">
       <c r="B24" s="43" t="inlineStr">
         <is>
-          <t>Mar-26</t>
+          <t>Apr-26</t>
         </is>
       </c>
       <c r="C24" s="43" t="inlineStr"/>
       <c r="D24" s="37" t="n">
-        <v>-0.005703109224023062</v>
+        <v>-0.03233392463753892</v>
       </c>
       <c r="E24" s="37" t="n">
-        <v>0.01048336746569301</v>
+        <v>0.003804826246388782</v>
       </c>
       <c r="F24" s="38" t="n">
-        <v>-0.5440150068846277</v>
+        <v>-8.498134354552338</v>
       </c>
       <c r="G24" s="44" t="n"/>
     </row>
@@ -1558,13 +1558,13 @@
       </c>
       <c r="C25" s="52" t="inlineStr"/>
       <c r="D25" s="41" t="n">
-        <v>0.005335527867341039</v>
+        <v>-0.03859917322048889</v>
       </c>
       <c r="E25" s="41" t="n">
-        <v>0.01159785506263344</v>
+        <v>0.0115104208368324</v>
       </c>
       <c r="F25" s="42" t="n">
-        <v>0.4600443649732537</v>
+        <v>-3.353411119163836</v>
       </c>
       <c r="G25" s="53" t="n"/>
     </row>
@@ -1577,13 +1577,13 @@
       </c>
       <c r="C26" s="52" t="inlineStr"/>
       <c r="D26" s="41" t="n">
-        <v>0.06621087281130533</v>
+        <v>0.01934883387499364</v>
       </c>
       <c r="E26" s="41" t="n">
-        <v>0.03528813776398843</v>
+        <v>0.03519865594435645</v>
       </c>
       <c r="F26" s="42" t="n">
-        <v>1.876292629952085</v>
+        <v>0.5497037700979581</v>
       </c>
       <c r="G26" s="53" t="n"/>
     </row>
@@ -1596,13 +1596,13 @@
       </c>
       <c r="C27" s="52" t="inlineStr"/>
       <c r="D27" s="41" t="n">
-        <v>0.05093302443721726</v>
+        <v>0.02089836032150494</v>
       </c>
       <c r="E27" s="41" t="n">
-        <v>0.03243902489712824</v>
+        <v>0.0380553842733744</v>
       </c>
       <c r="F27" s="42" t="n">
-        <v>1.570115766387486</v>
+        <v>0.5491564655182462</v>
       </c>
       <c r="G27" s="53" t="n"/>
     </row>
@@ -1634,13 +1634,13 @@
       </c>
       <c r="C29" s="52" t="inlineStr"/>
       <c r="D29" s="41" t="n">
-        <v>0.08336544777700006</v>
+        <v>0.05240389591600003</v>
       </c>
       <c r="E29" s="41" t="n">
-        <v>0.04043636873983614</v>
+        <v>0.0460962328228911</v>
       </c>
       <c r="F29" s="42" t="n">
-        <v>2.061645255867698</v>
+        <v>1.136836845590917</v>
       </c>
       <c r="G29" s="53" t="n"/>
     </row>
@@ -1668,7 +1668,7 @@
       <c r="C32" s="14" t="n"/>
       <c r="D32" s="14" t="n"/>
       <c r="E32" s="46" t="n">
-        <v>13242165.18089999</v>
+        <v>12863716.7165</v>
       </c>
       <c r="F32" s="29" t="n"/>
       <c r="G32" s="4" t="n"/>
@@ -1683,7 +1683,7 @@
       <c r="C33" s="14" t="n"/>
       <c r="D33" s="14" t="n"/>
       <c r="E33" s="46" t="n">
-        <v>12244542.28804657</v>
+        <v>12344315.64396385</v>
       </c>
       <c r="F33" s="29" t="n"/>
       <c r="G33" s="4" t="n"/>
@@ -1706,7 +1706,7 @@
       </c>
       <c r="C35" s="19" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="D35" s="20" t="n"/>
